--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/DistriAlunosClasseMT3serie_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/DistriAlunosClasseMT3serie_S3.xlsx
@@ -495,10 +495,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>1237</v>
+        <v>1924</v>
       </c>
       <c r="C10" t="n">
-        <v>4.157</v>
+        <v>6.465</v>
       </c>
     </row>
     <row r="11">
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>6246</v>
+        <v>6736</v>
       </c>
       <c r="C11" t="n">
-        <v>20.988</v>
+        <v>22.634</v>
       </c>
     </row>
     <row r="12">
@@ -517,10 +517,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>6207</v>
+        <v>5987</v>
       </c>
       <c r="C12" t="n">
-        <v>20.857</v>
+        <v>20.118</v>
       </c>
     </row>
     <row r="13">
@@ -528,10 +528,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>4545</v>
+        <v>4127</v>
       </c>
       <c r="C13" t="n">
-        <v>15.272</v>
+        <v>13.868</v>
       </c>
     </row>
     <row r="14">
@@ -539,10 +539,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>2770</v>
+        <v>2557</v>
       </c>
       <c r="C14" t="n">
-        <v>9.308</v>
+        <v>8.592</v>
       </c>
     </row>
     <row r="15">
@@ -550,10 +550,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>8755</v>
+        <v>8429</v>
       </c>
       <c r="C15" t="n">
-        <v>29.419</v>
+        <v>28.323</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/DistriAlunosClasseMT3serie_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/DistriAlunosClasseMT3serie_S3.xlsx
@@ -495,10 +495,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>1924</v>
+        <v>1333</v>
       </c>
       <c r="C10" t="n">
-        <v>6.465</v>
+        <v>4.479</v>
       </c>
     </row>
     <row r="11">
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>6736</v>
+        <v>6452</v>
       </c>
       <c r="C11" t="n">
-        <v>22.634</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="12">
@@ -517,10 +517,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>5987</v>
+        <v>6295</v>
       </c>
       <c r="C12" t="n">
-        <v>20.118</v>
+        <v>21.153</v>
       </c>
     </row>
     <row r="13">
@@ -528,10 +528,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>4127</v>
+        <v>4385</v>
       </c>
       <c r="C13" t="n">
-        <v>13.868</v>
+        <v>14.735</v>
       </c>
     </row>
     <row r="14">
@@ -539,10 +539,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>2557</v>
+        <v>2650</v>
       </c>
       <c r="C14" t="n">
-        <v>8.592</v>
+        <v>8.905</v>
       </c>
     </row>
     <row r="15">
@@ -550,10 +550,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>8429</v>
+        <v>8645</v>
       </c>
       <c r="C15" t="n">
-        <v>28.323</v>
+        <v>29.049</v>
       </c>
     </row>
   </sheetData>
